--- a/accounts.xlsx
+++ b/accounts.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Vins Official\teams\hybd\New folder\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Vins Official\teams\hybd\git\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF5C27A8-0E45-44FC-84A3-0F33EB342B17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDFF00D0-965B-429E-9AF4-C5A4FE8B6729}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="10800" xr2:uid="{60DAF7C2-9A1B-CB4D-9D5C-B3CE99ABDE91}"/>
   </bookViews>
@@ -137,10 +137,10 @@
     <t>shamilsham803@gmail.com</t>
   </si>
   <si>
-    <t xml:space="preserve"> Kunnath@7025</t>
-  </si>
-  <si>
     <t>shmlmilan@okhdfcbank</t>
+  </si>
+  <si>
+    <t>Kunnath@7025</t>
   </si>
 </sst>
 </file>
@@ -563,7 +563,7 @@
       <c r="A2" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C2" s="3" t="s">
@@ -699,18 +699,22 @@
       <c r="A10" t="s">
         <v>32</v>
       </c>
-      <c r="B10" t="s">
-        <v>33</v>
+      <c r="B10" s="1" t="s">
+        <v>34</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B10" r:id="rId1" xr:uid="{C45D14F6-35A1-4B25-9A92-71F42985C323}"/>
+    <hyperlink ref="B2" r:id="rId2" xr:uid="{E74D960F-E2D2-4AFC-9774-61A1FB31F4CC}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId3"/>
 </worksheet>
 </file>
--- a/accounts.xlsx
+++ b/accounts.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Vins Official\teams\hybd\git\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDFF00D0-965B-429E-9AF4-C5A4FE8B6729}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDA7D540-D9CD-4B5E-9DE6-573224DB0E15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="10800" xr2:uid="{60DAF7C2-9A1B-CB4D-9D5C-B3CE99ABDE91}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{60DAF7C2-9A1B-CB4D-9D5C-B3CE99ABDE91}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="28">
   <si>
     <t>username</t>
   </si>
@@ -53,101 +53,81 @@
     <t>upid</t>
   </si>
   <si>
-    <t>sunnysumod@gmail.com</t>
-  </si>
-  <si>
-    <t>Sumod@2204</t>
-  </si>
-  <si>
-    <t>Schreiben</t>
-  </si>
-  <si>
-    <t>sumodsunny@okicici</t>
-  </si>
-  <si>
-    <t>swetha6629@gmail.com</t>
-  </si>
-  <si>
-    <t>SwethaD@11</t>
-  </si>
-  <si>
-    <t>swetha6629@oksbi</t>
-  </si>
-  <si>
-    <t>ammuanakha49@gmail.com</t>
-  </si>
-  <si>
-    <t>anakha1256</t>
-  </si>
-  <si>
-    <t>ammuanakha49-1@oksbi</t>
-  </si>
-  <si>
-    <t>Schreiben, Sprechen</t>
-  </si>
-  <si>
-    <t>lincynebu@okhdfcbank</t>
-  </si>
-  <si>
-    <t>anujasvinu167@gmail.com</t>
-  </si>
-  <si>
-    <t>anujasvinu-3@okicici</t>
-  </si>
-  <si>
-    <t>aparnaajayalal93@gmail.com</t>
-  </si>
-  <si>
-    <t>aparnaajayalal@okaxis</t>
-  </si>
-  <si>
-    <t>lincynebu123@gmail.com</t>
-  </si>
-  <si>
-    <t>maria071</t>
-  </si>
-  <si>
-    <t>Bangtans</t>
-  </si>
-  <si>
-    <t>anuja2006s</t>
-  </si>
-  <si>
     <t xml:space="preserve">Amount </t>
   </si>
   <si>
-    <t>deepajoseph003@gmail.com</t>
-  </si>
-  <si>
-    <t>Josephdeepa@1</t>
-  </si>
-  <si>
-    <t>reshmasoman171@gmail.com</t>
-  </si>
-  <si>
-    <t>Achu@123</t>
-  </si>
-  <si>
-    <t>achurs97-2@okaxis</t>
-  </si>
-  <si>
-    <t>deejourumbil@oksbi</t>
-  </si>
-  <si>
-    <t>shamilsham803@gmail.com</t>
-  </si>
-  <si>
-    <t>shmlmilan@okhdfcbank</t>
-  </si>
-  <si>
-    <t>Kunnath@7025</t>
+    <t>aleenajose378@oksbi</t>
+  </si>
+  <si>
+    <t>aleenajose378@gmail.com</t>
+  </si>
+  <si>
+    <t>Aleena@aleena1</t>
+  </si>
+  <si>
+    <t>aleenaalina581@gmail.com</t>
+  </si>
+  <si>
+    <t>aleena@432</t>
+  </si>
+  <si>
+    <t>bthankachan595@okhdfcbank</t>
+  </si>
+  <si>
+    <t>rissaraju26@gmail.com</t>
+  </si>
+  <si>
+    <t>rissa2006</t>
+  </si>
+  <si>
+    <t>rissa4980@federal</t>
+  </si>
+  <si>
+    <t>aravindchandu018@gmail.com</t>
+  </si>
+  <si>
+    <t>9074431704@aA</t>
+  </si>
+  <si>
+    <t>aravindchandu018-1@okhdfcbank</t>
+  </si>
+  <si>
+    <t>sandraulloor@gmail.com</t>
+  </si>
+  <si>
+    <t>Christmas@37</t>
+  </si>
+  <si>
+    <t>8884038785@ybl</t>
+  </si>
+  <si>
+    <t>ashishrajesh2009@gmail.com</t>
+  </si>
+  <si>
+    <t>Saranya@2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+saranyaes13@okaxis</t>
+  </si>
+  <si>
+    <t>Schreiben,Sprechen</t>
+  </si>
+  <si>
+    <t>sahalanoushad063@gmail.com</t>
+  </si>
+  <si>
+    <t>SAHALA@2704</t>
+  </si>
+  <si>
+    <t>sahalanoushad294@oksbi</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
+  <fonts count="5">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -169,6 +149,18 @@
       <name val="JetBrains Mono"/>
       <family val="3"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -187,24 +179,168 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="2" xr:uid="{9E354A88-668C-4863-AA39-CA50F0BA6869}"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <dxfs count="12">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF6F8F9"/>
+          <bgColor rgb="FFF6F8F9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF356854"/>
+          <bgColor rgb="FF356854"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color rgb="FF356854"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF356854"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF356854"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF356854"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF6F8F9"/>
+          <bgColor rgb="FFF6F8F9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF356854"/>
+          <bgColor rgb="FF356854"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color rgb="FF356854"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF356854"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF356854"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF356854"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF6F8F9"/>
+          <bgColor rgb="FFF6F8F9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF356854"/>
+          <bgColor rgb="FF356854"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color rgb="FF356854"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF356854"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF356854"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF356854"/>
+        </bottom>
+      </border>
+    </dxf>
+  </dxfs>
+  <tableStyles count="3" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
+    <tableStyle name="Kochi-style" pivot="0" count="4" xr9:uid="{499236F8-518B-48BB-9B5C-D94801E9973C}">
+      <tableStyleElement type="wholeTable" size="0" dxfId="11"/>
+      <tableStyleElement type="headerRow" dxfId="10"/>
+      <tableStyleElement type="firstRowStripe" dxfId="9"/>
+      <tableStyleElement type="secondRowStripe" dxfId="8"/>
+    </tableStyle>
+    <tableStyle name="Hyderabad -style" pivot="0" count="4" xr9:uid="{E9EE0802-B97E-4581-9437-016DAE2A2FFB}">
+      <tableStyleElement type="wholeTable" size="0" dxfId="7"/>
+      <tableStyleElement type="headerRow" dxfId="6"/>
+      <tableStyleElement type="firstRowStripe" dxfId="5"/>
+      <tableStyleElement type="secondRowStripe" dxfId="4"/>
+    </tableStyle>
+    <tableStyle name="Kolhapur-style" pivot="0" count="4" xr9:uid="{C1F01944-4E46-4DD7-AFE0-A9BD04E80108}">
+      <tableStyleElement type="wholeTable" size="0" dxfId="3"/>
+      <tableStyleElement type="headerRow" dxfId="2"/>
+      <tableStyleElement type="firstRowStripe" dxfId="1"/>
+      <tableStyleElement type="secondRowStripe" dxfId="0"/>
+    </tableStyle>
+  </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -556,165 +692,116 @@
         <v>4</v>
       </c>
       <c r="E1" t="s">
-        <v>25</v>
+        <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>10</v>
+      <c r="A2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E2">
-        <v>4000</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="1" t="s">
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D4" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E3">
-        <v>4000</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C4" s="3" t="s">
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D4" t="s">
+      <c r="B5" s="3" t="s">
         <v>16</v>
-      </c>
-      <c r="E4">
-        <v>5400</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B5" t="s">
-        <v>24</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E5">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" t="s">
+      <c r="B6" s="3" t="s">
         <v>19</v>
-      </c>
-      <c r="B6" t="s">
-        <v>23</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="E6">
-        <v>5000</v>
-      </c>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>6</v>
+      <c r="A7" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>22</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E7">
-        <v>4700</v>
+        <v>3</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" t="s">
+      <c r="A8" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>26</v>
-      </c>
-      <c r="B8" t="s">
-        <v>27</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="D8" t="s">
-        <v>31</v>
-      </c>
-      <c r="E8">
-        <v>5000</v>
+      <c r="D8" s="3" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" t="s">
-        <v>28</v>
-      </c>
-      <c r="B9" t="s">
-        <v>29</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D9" t="s">
-        <v>30</v>
-      </c>
-      <c r="E9">
-        <v>6000</v>
-      </c>
+      <c r="C9" s="2"/>
     </row>
     <row r="10" spans="1:5">
-      <c r="A10" t="s">
-        <v>32</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D10" t="s">
-        <v>33</v>
-      </c>
+      <c r="B10" s="1"/>
+      <c r="C10" s="2"/>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="B10" r:id="rId1" xr:uid="{C45D14F6-35A1-4B25-9A92-71F42985C323}"/>
-    <hyperlink ref="B2" r:id="rId2" xr:uid="{E74D960F-E2D2-4AFC-9774-61A1FB31F4CC}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>